--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_07-11-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_07-11-2025.xlsx
@@ -538,37 +538,37 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>£9.75</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>£9.75</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>£9.75</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>£9.92</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>£9.83</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>£9.89</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
         <is>
           <t>£9.83</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>£9.83</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>£9.92</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>£9.83</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>£9.89</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>£9.84</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -592,23 +592,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6b6ee7a05
-	0x7ff6b6ee7a60
-	0x7ff6b6c616ad
-	0x7ff6b6cba13e
-	0x7ff6b6cba44c
-	0x7ff6b6d0ebe7
-	0x7ff6b6d0b8fb
-	0x7ff6b6cab068
-	0x7ff6b6cabe93
-	0x7ff6b71a29a0
-	0x7ff6b719ce20
-	0x7ff6b71bcc15
-	0x7ff6b6f0309e
-	0x7ff6b6f0ad8f
-	0x7ff6b6ef0be4
-	0x7ff6b6ef0d9f
-	0x7ff6b6ed67f8
+	0x7ff7fafc7a05
+	0x7ff7fafc7a60
+	0x7ff7fad416ad
+	0x7ff7fad9a13e
+	0x7ff7fad9a44c
+	0x7ff7fadeebe7
+	0x7ff7fadeb8fb
+	0x7ff7fad8b068
+	0x7ff7fad8be93
+	0x7ff7fb2829a0
+	0x7ff7fb27ce20
+	0x7ff7fb29cc15
+	0x7ff7fafe309e
+	0x7ff7fafead8f
+	0x7ff7fafd0be4
+	0x7ff7fafd0d9f
+	0x7ff7fafb67f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
@@ -658,17 +658,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>£11.15</t>
+          <t>£11.10</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>£11.15</t>
+          <t>£11.10</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>£11.15</t>
+          <t>£11.10</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -712,23 +712,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6b6ee7a05
-	0x7ff6b6ee7a60
-	0x7ff6b6c616ad
-	0x7ff6b6cba13e
-	0x7ff6b6cba44c
-	0x7ff6b6d0ebe7
-	0x7ff6b6d0b8fb
-	0x7ff6b6cab068
-	0x7ff6b6cabe93
-	0x7ff6b71a29a0
-	0x7ff6b719ce20
-	0x7ff6b71bcc15
-	0x7ff6b6f0309e
-	0x7ff6b6f0ad8f
-	0x7ff6b6ef0be4
-	0x7ff6b6ef0d9f
-	0x7ff6b6ed67f8
+	0x7ff7fafc7a05
+	0x7ff7fafc7a60
+	0x7ff7fad416ad
+	0x7ff7fad9a13e
+	0x7ff7fad9a44c
+	0x7ff7fadeebe7
+	0x7ff7fadeb8fb
+	0x7ff7fad8b068
+	0x7ff7fad8be93
+	0x7ff7fb2829a0
+	0x7ff7fb27ce20
+	0x7ff7fb29cc15
+	0x7ff7fafe309e
+	0x7ff7fafead8f
+	0x7ff7fafd0be4
+	0x7ff7fafd0d9f
+	0x7ff7fafb67f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
@@ -832,23 +832,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6b6ee7a05
-	0x7ff6b6ee7a60
-	0x7ff6b6c616ad
-	0x7ff6b6cba13e
-	0x7ff6b6cba44c
-	0x7ff6b6d0ebe7
-	0x7ff6b6d0b8fb
-	0x7ff6b6cab068
-	0x7ff6b6cabe93
-	0x7ff6b71a29a0
-	0x7ff6b719ce20
-	0x7ff6b71bcc15
-	0x7ff6b6f0309e
-	0x7ff6b6f0ad8f
-	0x7ff6b6ef0be4
-	0x7ff6b6ef0d9f
-	0x7ff6b6ed67f8
+	0x7ff7fafc7a05
+	0x7ff7fafc7a60
+	0x7ff7fad416ad
+	0x7ff7fad9a13e
+	0x7ff7fad9a44c
+	0x7ff7fadeebe7
+	0x7ff7fadeb8fb
+	0x7ff7fad8b068
+	0x7ff7fad8be93
+	0x7ff7fb2829a0
+	0x7ff7fb27ce20
+	0x7ff7fb29cc15
+	0x7ff7fafe309e
+	0x7ff7fafead8f
+	0x7ff7fafd0be4
+	0x7ff7fafd0d9f
+	0x7ff7fafb67f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
@@ -898,17 +898,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>£14.73</t>
+          <t>£14.60</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>£14.73</t>
+          <t>£14.60</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>£14.73</t>
+          <t>£14.60</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -952,23 +952,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6b6ee7a05
-	0x7ff6b6ee7a60
-	0x7ff6b6c616ad
-	0x7ff6b6cba13e
-	0x7ff6b6cba44c
-	0x7ff6b6d0ebe7
-	0x7ff6b6d0b8fb
-	0x7ff6b6cab068
-	0x7ff6b6cabe93
-	0x7ff6b71a29a0
-	0x7ff6b719ce20
-	0x7ff6b71bcc15
-	0x7ff6b6f0309e
-	0x7ff6b6f0ad8f
-	0x7ff6b6ef0be4
-	0x7ff6b6ef0d9f
-	0x7ff6b6ed67f8
+	0x7ff7fafc7a05
+	0x7ff7fafc7a60
+	0x7ff7fad416ad
+	0x7ff7fad9a13e
+	0x7ff7fad9a44c
+	0x7ff7fadeebe7
+	0x7ff7fadeb8fb
+	0x7ff7fad8b068
+	0x7ff7fad8be93
+	0x7ff7fb2829a0
+	0x7ff7fb27ce20
+	0x7ff7fb29cc15
+	0x7ff7fafe309e
+	0x7ff7fafead8f
+	0x7ff7fafd0be4
+	0x7ff7fafd0d9f
+	0x7ff7fafb67f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
@@ -1072,23 +1072,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6b6ee7a05
-	0x7ff6b6ee7a60
-	0x7ff6b6c616ad
-	0x7ff6b6cba13e
-	0x7ff6b6cba44c
-	0x7ff6b6d0ebe7
-	0x7ff6b6d0b8fb
-	0x7ff6b6cab068
-	0x7ff6b6cabe93
-	0x7ff6b71a29a0
-	0x7ff6b719ce20
-	0x7ff6b71bcc15
-	0x7ff6b6f0309e
-	0x7ff6b6f0ad8f
-	0x7ff6b6ef0be4
-	0x7ff6b6ef0d9f
-	0x7ff6b6ed67f8
+	0x7ff7fafc7a05
+	0x7ff7fafc7a60
+	0x7ff7fad416ad
+	0x7ff7fad9a13e
+	0x7ff7fad9a44c
+	0x7ff7fadeebe7
+	0x7ff7fadeb8fb
+	0x7ff7fad8b068
+	0x7ff7fad8be93
+	0x7ff7fb2829a0
+	0x7ff7fb27ce20
+	0x7ff7fb29cc15
+	0x7ff7fafe309e
+	0x7ff7fafead8f
+	0x7ff7fafd0be4
+	0x7ff7fafd0d9f
+	0x7ff7fafb67f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
@@ -1138,17 +1138,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>£20.50</t>
+          <t>£20.25</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>£20.50</t>
+          <t>£20.25</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>£20.50</t>
+          <t>£20.25</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1192,23 +1192,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6b6ee7a05
-	0x7ff6b6ee7a60
-	0x7ff6b6c616ad
-	0x7ff6b6cba13e
-	0x7ff6b6cba44c
-	0x7ff6b6d0ebe7
-	0x7ff6b6d0b8fb
-	0x7ff6b6cab068
-	0x7ff6b6cabe93
-	0x7ff6b71a29a0
-	0x7ff6b719ce20
-	0x7ff6b71bcc15
-	0x7ff6b6f0309e
-	0x7ff6b6f0ad8f
-	0x7ff6b6ef0be4
-	0x7ff6b6ef0d9f
-	0x7ff6b6ed67f8
+	0x7ff7fafc7a05
+	0x7ff7fafc7a60
+	0x7ff7fad416ad
+	0x7ff7fad9a13e
+	0x7ff7fad9a44c
+	0x7ff7fadeebe7
+	0x7ff7fadeb8fb
+	0x7ff7fad8b068
+	0x7ff7fad8be93
+	0x7ff7fb2829a0
+	0x7ff7fb27ce20
+	0x7ff7fb29cc15
+	0x7ff7fafe309e
+	0x7ff7fafead8f
+	0x7ff7fafd0be4
+	0x7ff7fafd0d9f
+	0x7ff7fafb67f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
@@ -1258,17 +1258,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>£20.55</t>
+          <t>£20.47</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>£20.55</t>
+          <t>£20.47</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>£20.55</t>
+          <t>£20.47</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1312,23 +1312,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6b6ee7a05
-	0x7ff6b6ee7a60
-	0x7ff6b6c616ad
-	0x7ff6b6cba13e
-	0x7ff6b6cba44c
-	0x7ff6b6d0ebe7
-	0x7ff6b6d0b8fb
-	0x7ff6b6cab068
-	0x7ff6b6cabe93
-	0x7ff6b71a29a0
-	0x7ff6b719ce20
-	0x7ff6b71bcc15
-	0x7ff6b6f0309e
-	0x7ff6b6f0ad8f
-	0x7ff6b6ef0be4
-	0x7ff6b6ef0d9f
-	0x7ff6b6ed67f8
+	0x7ff7fafc7a05
+	0x7ff7fafc7a60
+	0x7ff7fad416ad
+	0x7ff7fad9a13e
+	0x7ff7fad9a44c
+	0x7ff7fadeebe7
+	0x7ff7fadeb8fb
+	0x7ff7fad8b068
+	0x7ff7fad8be93
+	0x7ff7fb2829a0
+	0x7ff7fb27ce20
+	0x7ff7fb29cc15
+	0x7ff7fafe309e
+	0x7ff7fafead8f
+	0x7ff7fafd0be4
+	0x7ff7fafd0d9f
+	0x7ff7fafb67f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
@@ -1378,24 +1378,24 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>£23.45</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>£23.45</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>£23.45</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>£23.75</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>£23.75</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>£23.75</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>£23.75</t>
-        </is>
-      </c>
       <c r="G9" t="inlineStr">
         <is>
           <t>£23.51</t>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>£23.72</t>
+          <t>£23.66</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1432,23 +1432,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6b6ee7a05
-	0x7ff6b6ee7a60
-	0x7ff6b6c616ad
-	0x7ff6b6cba13e
-	0x7ff6b6cba44c
-	0x7ff6b6d0ebe7
-	0x7ff6b6d0b8fb
-	0x7ff6b6cab068
-	0x7ff6b6cabe93
-	0x7ff6b71a29a0
-	0x7ff6b719ce20
-	0x7ff6b71bcc15
-	0x7ff6b6f0309e
-	0x7ff6b6f0ad8f
-	0x7ff6b6ef0be4
-	0x7ff6b6ef0d9f
-	0x7ff6b6ed67f8
+	0x7ff7fafc7a05
+	0x7ff7fafc7a60
+	0x7ff7fad416ad
+	0x7ff7fad9a13e
+	0x7ff7fad9a44c
+	0x7ff7fadeebe7
+	0x7ff7fadeb8fb
+	0x7ff7fad8b068
+	0x7ff7fad8be93
+	0x7ff7fb2829a0
+	0x7ff7fb27ce20
+	0x7ff7fb29cc15
+	0x7ff7fafe309e
+	0x7ff7fafead8f
+	0x7ff7fafd0be4
+	0x7ff7fafd0d9f
+	0x7ff7fafb67f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>£38.36</t>
+          <t>Error: 503 Server Error: Service Unavailable for url: https://www.insulationshop.co/80mm_celotex_ga4000_pir_insulation.html</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1498,17 +1498,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>£25.75</t>
+          <t>£25.45</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>£25.75</t>
+          <t>£25.45</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>£25.75</t>
+          <t>£25.45</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1552,23 +1552,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6b6ee7a05
-	0x7ff6b6ee7a60
-	0x7ff6b6c616ad
-	0x7ff6b6cba13e
-	0x7ff6b6cba44c
-	0x7ff6b6d0ebe7
-	0x7ff6b6d0b8fb
-	0x7ff6b6cab068
-	0x7ff6b6cabe93
-	0x7ff6b71a29a0
-	0x7ff6b719ce20
-	0x7ff6b71bcc15
-	0x7ff6b6f0309e
-	0x7ff6b6f0ad8f
-	0x7ff6b6ef0be4
-	0x7ff6b6ef0d9f
-	0x7ff6b6ed67f8
+	0x7ff7fafc7a05
+	0x7ff7fafc7a60
+	0x7ff7fad416ad
+	0x7ff7fad9a13e
+	0x7ff7fad9a44c
+	0x7ff7fadeebe7
+	0x7ff7fadeb8fb
+	0x7ff7fad8b068
+	0x7ff7fad8be93
+	0x7ff7fb2829a0
+	0x7ff7fb27ce20
+	0x7ff7fb29cc15
+	0x7ff7fafe309e
+	0x7ff7fafead8f
+	0x7ff7fafd0be4
+	0x7ff7fafd0d9f
+	0x7ff7fafb67f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
@@ -1618,17 +1618,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>£25.25</t>
+          <t>£25.20</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>£25.25</t>
+          <t>£25.20</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>£25.25</t>
+          <t>£25.20</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1672,23 +1672,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6b6ee7a05
-	0x7ff6b6ee7a60
-	0x7ff6b6c616ad
-	0x7ff6b6cba13e
-	0x7ff6b6cba44c
-	0x7ff6b6d0ebe7
-	0x7ff6b6d0b8fb
-	0x7ff6b6cab068
-	0x7ff6b6cabe93
-	0x7ff6b71a29a0
-	0x7ff6b719ce20
-	0x7ff6b71bcc15
-	0x7ff6b6f0309e
-	0x7ff6b6f0ad8f
-	0x7ff6b6ef0be4
-	0x7ff6b6ef0d9f
-	0x7ff6b6ed67f8
+	0x7ff7fafc7a05
+	0x7ff7fafc7a60
+	0x7ff7fad416ad
+	0x7ff7fad9a13e
+	0x7ff7fad9a44c
+	0x7ff7fadeebe7
+	0x7ff7fadeb8fb
+	0x7ff7fad8b068
+	0x7ff7fad8be93
+	0x7ff7fb2829a0
+	0x7ff7fb27ce20
+	0x7ff7fb29cc15
+	0x7ff7fafe309e
+	0x7ff7fafead8f
+	0x7ff7fafd0be4
+	0x7ff7fafd0d9f
+	0x7ff7fafb67f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
@@ -1792,23 +1792,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6b6ee7a05
-	0x7ff6b6ee7a60
-	0x7ff6b6c616ad
-	0x7ff6b6cba13e
-	0x7ff6b6cba44c
-	0x7ff6b6d0ebe7
-	0x7ff6b6d0b8fb
-	0x7ff6b6cab068
-	0x7ff6b6cabe93
-	0x7ff6b71a29a0
-	0x7ff6b719ce20
-	0x7ff6b71bcc15
-	0x7ff6b6f0309e
-	0x7ff6b6f0ad8f
-	0x7ff6b6ef0be4
-	0x7ff6b6ef0d9f
-	0x7ff6b6ed67f8
+	0x7ff7fafc7a05
+	0x7ff7fafc7a60
+	0x7ff7fad416ad
+	0x7ff7fad9a13e
+	0x7ff7fad9a44c
+	0x7ff7fadeebe7
+	0x7ff7fadeb8fb
+	0x7ff7fad8b068
+	0x7ff7fad8be93
+	0x7ff7fb2829a0
+	0x7ff7fb27ce20
+	0x7ff7fb29cc15
+	0x7ff7fafe309e
+	0x7ff7fafead8f
+	0x7ff7fafd0be4
+	0x7ff7fafd0d9f
+	0x7ff7fafb67f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
@@ -1858,17 +1858,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>£31.00</t>
+          <t>£30.75</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>£31.00</t>
+          <t>£30.75</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>£31.00</t>
+          <t>£30.75</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1912,23 +1912,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6b6ee7a05
-	0x7ff6b6ee7a60
-	0x7ff6b6c616ad
-	0x7ff6b6cba13e
-	0x7ff6b6cba44c
-	0x7ff6b6d0ebe7
-	0x7ff6b6d0b8fb
-	0x7ff6b6cab068
-	0x7ff6b6cabe93
-	0x7ff6b71a29a0
-	0x7ff6b719ce20
-	0x7ff6b71bcc15
-	0x7ff6b6f0309e
-	0x7ff6b6f0ad8f
-	0x7ff6b6ef0be4
-	0x7ff6b6ef0d9f
-	0x7ff6b6ed67f8
+	0x7ff7fafc7a05
+	0x7ff7fafc7a60
+	0x7ff7fad416ad
+	0x7ff7fad9a13e
+	0x7ff7fad9a44c
+	0x7ff7fadeebe7
+	0x7ff7fadeb8fb
+	0x7ff7fad8b068
+	0x7ff7fad8be93
+	0x7ff7fb2829a0
+	0x7ff7fb27ce20
+	0x7ff7fb29cc15
+	0x7ff7fafe309e
+	0x7ff7fafead8f
+	0x7ff7fafd0be4
+	0x7ff7fafd0d9f
+	0x7ff7fafb67f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
@@ -1978,17 +1978,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>£38.30</t>
+          <t>£38.05</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>£38.30</t>
+          <t>£38.05</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>£38.30</t>
+          <t>£38.05</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -2032,23 +2032,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6b6ee7a05
-	0x7ff6b6ee7a60
-	0x7ff6b6c616ad
-	0x7ff6b6cba13e
-	0x7ff6b6cba44c
-	0x7ff6b6d0ebe7
-	0x7ff6b6d0b8fb
-	0x7ff6b6cab068
-	0x7ff6b6cabe93
-	0x7ff6b71a29a0
-	0x7ff6b719ce20
-	0x7ff6b71bcc15
-	0x7ff6b6f0309e
-	0x7ff6b6f0ad8f
-	0x7ff6b6ef0be4
-	0x7ff6b6ef0d9f
-	0x7ff6b6ed67f8
+	0x7ff7fafc7a05
+	0x7ff7fafc7a60
+	0x7ff7fad416ad
+	0x7ff7fad9a13e
+	0x7ff7fad9a44c
+	0x7ff7fadeebe7
+	0x7ff7fadeb8fb
+	0x7ff7fad8b068
+	0x7ff7fad8be93
+	0x7ff7fb2829a0
+	0x7ff7fb27ce20
+	0x7ff7fb29cc15
+	0x7ff7fafe309e
+	0x7ff7fafead8f
+	0x7ff7fafd0be4
+	0x7ff7fafd0d9f
+	0x7ff7fafb67f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
@@ -2128,7 +2128,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>£38.22</t>
+          <t>£38.21</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2152,23 +2152,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6b6ee7a05
-	0x7ff6b6ee7a60
-	0x7ff6b6c616ad
-	0x7ff6b6cba13e
-	0x7ff6b6cba44c
-	0x7ff6b6d0ebe7
-	0x7ff6b6d0b8fb
-	0x7ff6b6cab068
-	0x7ff6b6cabe93
-	0x7ff6b71a29a0
-	0x7ff6b719ce20
-	0x7ff6b71bcc15
-	0x7ff6b6f0309e
-	0x7ff6b6f0ad8f
-	0x7ff6b6ef0be4
-	0x7ff6b6ef0d9f
-	0x7ff6b6ed67f8
+	0x7ff683127a05
+	0x7ff683127a60
+	0x7ff682ea16ad
+	0x7ff682efa13e
+	0x7ff682efa44c
+	0x7ff682f4ebe7
+	0x7ff682f4b8fb
+	0x7ff682eeb068
+	0x7ff682eebe93
+	0x7ff6833e29a0
+	0x7ff6833dce20
+	0x7ff6833fcc15
+	0x7ff68314309e
+	0x7ff68314ad8f
+	0x7ff683130be4
+	0x7ff683130d9f
+	0x7ff6831167f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
@@ -2272,23 +2272,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6b6ee7a05
-	0x7ff6b6ee7a60
-	0x7ff6b6c616ad
-	0x7ff6b6cba13e
-	0x7ff6b6cba44c
-	0x7ff6b6d0ebe7
-	0x7ff6b6d0b8fb
-	0x7ff6b6cab068
-	0x7ff6b6cabe93
-	0x7ff6b71a29a0
-	0x7ff6b719ce20
-	0x7ff6b71bcc15
-	0x7ff6b6f0309e
-	0x7ff6b6f0ad8f
-	0x7ff6b6ef0be4
-	0x7ff6b6ef0d9f
-	0x7ff6b6ed67f8
+	0x7ff658287a05
+	0x7ff658287a60
+	0x7ff6580016ad
+	0x7ff65805a13e
+	0x7ff65805a44c
+	0x7ff6580aebe7
+	0x7ff6580ab8fb
+	0x7ff65804b068
+	0x7ff65804be93
+	0x7ff6585429a0
+	0x7ff65853ce20
+	0x7ff65855cc15
+	0x7ff6582a309e
+	0x7ff6582aad8f
+	0x7ff658290be4
+	0x7ff658290d9f
+	0x7ff6582767f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
@@ -2489,23 +2489,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6b6ee7a05
-	0x7ff6b6ee7a60
-	0x7ff6b6c616ad
-	0x7ff6b6cba13e
-	0x7ff6b6cba44c
-	0x7ff6b6d0ebe7
-	0x7ff6b6d0b8fb
-	0x7ff6b6cab068
-	0x7ff6b6cabe93
-	0x7ff6b71a29a0
-	0x7ff6b719ce20
-	0x7ff6b71bcc15
-	0x7ff6b6f0309e
-	0x7ff6b6f0ad8f
-	0x7ff6b6ef0be4
-	0x7ff6b6ef0d9f
-	0x7ff6b6ed67f8
+	0x7ff658287a05
+	0x7ff658287a60
+	0x7ff6580016ad
+	0x7ff65805a13e
+	0x7ff65805a44c
+	0x7ff6580aebe7
+	0x7ff6580ab8fb
+	0x7ff65804b068
+	0x7ff65804be93
+	0x7ff6585429a0
+	0x7ff65853ce20
+	0x7ff65855cc15
+	0x7ff6582a309e
+	0x7ff6582aad8f
+	0x7ff658290be4
+	0x7ff658290d9f
+	0x7ff6582767f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
@@ -2555,17 +2555,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>£28.10</t>
+          <t>£27.65</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>£28.10</t>
+          <t>£27.65</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>£28.10</t>
+          <t>£27.65</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2609,23 +2609,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6b6ee7a05
-	0x7ff6b6ee7a60
-	0x7ff6b6c616ad
-	0x7ff6b6cba13e
-	0x7ff6b6cba44c
-	0x7ff6b6d0ebe7
-	0x7ff6b6d0b8fb
-	0x7ff6b6cab068
-	0x7ff6b6cabe93
-	0x7ff6b71a29a0
-	0x7ff6b719ce20
-	0x7ff6b71bcc15
-	0x7ff6b6f0309e
-	0x7ff6b6f0ad8f
-	0x7ff6b6ef0be4
-	0x7ff6b6ef0d9f
-	0x7ff6b6ed67f8
+	0x7ff658287a05
+	0x7ff658287a60
+	0x7ff6580016ad
+	0x7ff65805a13e
+	0x7ff65805a44c
+	0x7ff6580aebe7
+	0x7ff6580ab8fb
+	0x7ff65804b068
+	0x7ff65804be93
+	0x7ff6585429a0
+	0x7ff65853ce20
+	0x7ff65855cc15
+	0x7ff6582a309e
+	0x7ff6582aad8f
+	0x7ff658290be4
+	0x7ff658290d9f
+	0x7ff6582767f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
@@ -2675,17 +2675,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>£33.94</t>
+          <t>£33.65</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>£33.94</t>
+          <t>£33.65</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>£33.94</t>
+          <t>£33.65</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2729,23 +2729,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6b6ee7a05
-	0x7ff6b6ee7a60
-	0x7ff6b6c616ad
-	0x7ff6b6cba13e
-	0x7ff6b6cba44c
-	0x7ff6b6d0ebe7
-	0x7ff6b6d0b8fb
-	0x7ff6b6cab068
-	0x7ff6b6cabe93
-	0x7ff6b71a29a0
-	0x7ff6b719ce20
-	0x7ff6b71bcc15
-	0x7ff6b6f0309e
-	0x7ff6b6f0ad8f
-	0x7ff6b6ef0be4
-	0x7ff6b6ef0d9f
-	0x7ff6b6ed67f8
+	0x7ff658287a05
+	0x7ff658287a60
+	0x7ff6580016ad
+	0x7ff65805a13e
+	0x7ff65805a44c
+	0x7ff6580aebe7
+	0x7ff6580ab8fb
+	0x7ff65804b068
+	0x7ff65804be93
+	0x7ff6585429a0
+	0x7ff65853ce20
+	0x7ff65855cc15
+	0x7ff6582a309e
+	0x7ff6582aad8f
+	0x7ff658290be4
+	0x7ff658290d9f
+	0x7ff6582767f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
@@ -2825,7 +2825,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>£37.05</t>
+          <t>£36.61</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2849,23 +2849,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6b6ee7a05
-	0x7ff6b6ee7a60
-	0x7ff6b6c616ad
-	0x7ff6b6cba13e
-	0x7ff6b6cba44c
-	0x7ff6b6d0ebe7
-	0x7ff6b6d0b8fb
-	0x7ff6b6cab068
-	0x7ff6b6cabe93
-	0x7ff6b71a29a0
-	0x7ff6b719ce20
-	0x7ff6b71bcc15
-	0x7ff6b6f0309e
-	0x7ff6b6f0ad8f
-	0x7ff6b6ef0be4
-	0x7ff6b6ef0d9f
-	0x7ff6b6ed67f8
+	0x7ff658287a05
+	0x7ff658287a60
+	0x7ff6580016ad
+	0x7ff65805a13e
+	0x7ff65805a44c
+	0x7ff6580aebe7
+	0x7ff6580ab8fb
+	0x7ff65804b068
+	0x7ff65804be93
+	0x7ff6585429a0
+	0x7ff65853ce20
+	0x7ff65855cc15
+	0x7ff6582a309e
+	0x7ff6582aad8f
+	0x7ff658290be4
+	0x7ff658290d9f
+	0x7ff6582767f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
@@ -2915,17 +2915,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>£42.00</t>
+          <t>£41.00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>£42.00</t>
+          <t>£41.00</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>£42.00</t>
+          <t>£41.00</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2969,23 +2969,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6b6ee7a05
-	0x7ff6b6ee7a60
-	0x7ff6b6c616ad
-	0x7ff6b6cba13e
-	0x7ff6b6cba44c
-	0x7ff6b6d0ebe7
-	0x7ff6b6d0b8fb
-	0x7ff6b6cab068
-	0x7ff6b6cabe93
-	0x7ff6b71a29a0
-	0x7ff6b719ce20
-	0x7ff6b71bcc15
-	0x7ff6b6f0309e
-	0x7ff6b6f0ad8f
-	0x7ff6b6ef0be4
-	0x7ff6b6ef0d9f
-	0x7ff6b6ed67f8
+	0x7ff658287a05
+	0x7ff658287a60
+	0x7ff6580016ad
+	0x7ff65805a13e
+	0x7ff65805a44c
+	0x7ff6580aebe7
+	0x7ff6580ab8fb
+	0x7ff65804b068
+	0x7ff65804be93
+	0x7ff6585429a0
+	0x7ff65853ce20
+	0x7ff65855cc15
+	0x7ff6582a309e
+	0x7ff6582aad8f
+	0x7ff658290be4
+	0x7ff658290d9f
+	0x7ff6582767f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
@@ -3089,23 +3089,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6b6ee7a05
-	0x7ff6b6ee7a60
-	0x7ff6b6c616ad
-	0x7ff6b6cba13e
-	0x7ff6b6cba44c
-	0x7ff6b6d0ebe7
-	0x7ff6b6d0b8fb
-	0x7ff6b6cab068
-	0x7ff6b6cabe93
-	0x7ff6b71a29a0
-	0x7ff6b719ce20
-	0x7ff6b71bcc15
-	0x7ff6b6f0309e
-	0x7ff6b6f0ad8f
-	0x7ff6b6ef0be4
-	0x7ff6b6ef0d9f
-	0x7ff6b6ed67f8
+	0x7ff658287a05
+	0x7ff658287a60
+	0x7ff6580016ad
+	0x7ff65805a13e
+	0x7ff65805a44c
+	0x7ff6580aebe7
+	0x7ff6580ab8fb
+	0x7ff65804b068
+	0x7ff65804be93
+	0x7ff6585429a0
+	0x7ff65853ce20
+	0x7ff65855cc15
+	0x7ff6582a309e
+	0x7ff6582aad8f
+	0x7ff658290be4
+	0x7ff658290d9f
+	0x7ff6582767f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
@@ -3209,23 +3209,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6b6ee7a05
-	0x7ff6b6ee7a60
-	0x7ff6b6c616ad
-	0x7ff6b6cba13e
-	0x7ff6b6cba44c
-	0x7ff6b6d0ebe7
-	0x7ff6b6d0b8fb
-	0x7ff6b6cab068
-	0x7ff6b6cabe93
-	0x7ff6b71a29a0
-	0x7ff6b719ce20
-	0x7ff6b71bcc15
-	0x7ff6b6f0309e
-	0x7ff6b6f0ad8f
-	0x7ff6b6ef0be4
-	0x7ff6b6ef0d9f
-	0x7ff6b6ed67f8
+	0x7ff658287a05
+	0x7ff658287a60
+	0x7ff6580016ad
+	0x7ff65805a13e
+	0x7ff65805a44c
+	0x7ff6580aebe7
+	0x7ff6580ab8fb
+	0x7ff65804b068
+	0x7ff65804be93
+	0x7ff6585429a0
+	0x7ff65853ce20
+	0x7ff65855cc15
+	0x7ff6582a309e
+	0x7ff6582aad8f
+	0x7ff658290be4
+	0x7ff658290d9f
+	0x7ff6582767f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
@@ -3329,23 +3329,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6b6ee7a05
-	0x7ff6b6ee7a60
-	0x7ff6b6c616ad
-	0x7ff6b6cba13e
-	0x7ff6b6cba44c
-	0x7ff6b6d0ebe7
-	0x7ff6b6d0b8fb
-	0x7ff6b6cab068
-	0x7ff6b6cabe93
-	0x7ff6b71a29a0
-	0x7ff6b719ce20
-	0x7ff6b71bcc15
-	0x7ff6b6f0309e
-	0x7ff6b6f0ad8f
-	0x7ff6b6ef0be4
-	0x7ff6b6ef0d9f
-	0x7ff6b6ed67f8
+	0x7ff66ff57a05
+	0x7ff66ff57a60
+	0x7ff66fcd16ad
+	0x7ff66fd2a13e
+	0x7ff66fd2a44c
+	0x7ff66fd7ebe7
+	0x7ff66fd7b8fb
+	0x7ff66fd1b068
+	0x7ff66fd1be93
+	0x7ff6702129a0
+	0x7ff67020ce20
+	0x7ff67022cc15
+	0x7ff66ff7309e
+	0x7ff66ff7ad8f
+	0x7ff66ff60be4
+	0x7ff66ff60d9f
+	0x7ff66ff467f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
@@ -3449,23 +3449,23 @@
   (Session info: chrome=142.0.7444.60); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6b6ee7a05
-	0x7ff6b6ee7a60
-	0x7ff6b6c616ad
-	0x7ff6b6cba13e
-	0x7ff6b6cba44c
-	0x7ff6b6d0ebe7
-	0x7ff6b6d0b8fb
-	0x7ff6b6cab068
-	0x7ff6b6cabe93
-	0x7ff6b71a29a0
-	0x7ff6b719ce20
-	0x7ff6b71bcc15
-	0x7ff6b6f0309e
-	0x7ff6b6f0ad8f
-	0x7ff6b6ef0be4
-	0x7ff6b6ef0d9f
-	0x7ff6b6ed67f8
+	0x7ff66ff57a05
+	0x7ff66ff57a60
+	0x7ff66fcd16ad
+	0x7ff66fd2a13e
+	0x7ff66fd2a44c
+	0x7ff66fd7ebe7
+	0x7ff66fd7b8fb
+	0x7ff66fd1b068
+	0x7ff66fd1be93
+	0x7ff6702129a0
+	0x7ff67020ce20
+	0x7ff67022cc15
+	0x7ff66ff7309e
+	0x7ff66ff7ad8f
+	0x7ff66ff60be4
+	0x7ff66ff60d9f
+	0x7ff66ff467f8
 	0x7ff8c8a7e8d7
 	0x7ff8c9fac53c
 </t>
